--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:35</t>
+    <t xml:space="preserve">2026-09-09 22:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:21</t>
+    <t xml:space="preserve">2026-09-12 19:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:38</t>
+    <t xml:space="preserve">2026-09-24 00:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:15</t>
+    <t xml:space="preserve">2026-09-27 22:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:05</t>
+    <t xml:space="preserve">2026-09-29 10:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2019</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>25.82</v>
+        <v>258.23</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +525,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>24.73</v>
+        <v>247.3</v>
       </c>
     </row>
     <row r="4">
@@ -542,7 +542,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>24.16</v>
+        <v>241.6</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +559,7 @@
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>17.07</v>
+        <v>170.74</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>16.75</v>
+        <v>167.53</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>16.17</v>
+        <v>161.72</v>
       </c>
     </row>
     <row r="8">
@@ -610,7 +610,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>14.79</v>
+        <v>147.89</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>14.24</v>
+        <v>142.42</v>
       </c>
     </row>
     <row r="10">
@@ -644,7 +644,7 @@
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>11.22</v>
+        <v>112.17</v>
       </c>
     </row>
     <row r="11">
@@ -661,7 +661,7 @@
         <v>2019</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>8.85</v>
+        <v>88.53</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 10:59</t>
+    <t xml:space="preserve">2026-10-01 19:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:24</t>
+    <t xml:space="preserve">2026-10-02 13:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:09</t>
+    <t xml:space="preserve">2026-10-04 07:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 07:53</t>
+    <t xml:space="preserve">2026-10-05 07:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
